--- a/SECS Data Collection Specification Rev1.0_GRV-810AW-1224.xlsx
+++ b/SECS Data Collection Specification Rev1.0_GRV-810AW-1224.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6514" uniqueCount="3298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="3299">
   <si>
     <t>Description</t>
   </si>
@@ -20407,6 +20407,10 @@
   <si>
     <t>1. 刪除不必要SV</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="32" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -21610,40 +21614,6 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="6" applyBorder="1"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -21653,6 +21623,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -21685,6 +21658,37 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="6" applyBorder="1"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -22457,7 +22461,7 @@
         <xdr:cNvPr id="3" name="文本框 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22897,7 +22901,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -49023,140 +49027,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.25" thickBot="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="153"/>
     </row>
     <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="149"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="163"/>
     </row>
     <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="164" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="136"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="151"/>
+      <c r="A4" s="165"/>
       <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" thickBot="1">
-      <c r="A5" s="140" t="s">
+      <c r="A5" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="141"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="144"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="158"/>
     </row>
     <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="158" t="s">
+      <c r="A6" s="143" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="160"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="162"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="147"/>
     </row>
     <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="158"/>
+      <c r="A7" s="143"/>
       <c r="B7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="152"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="154"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="136"/>
     </row>
     <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="158"/>
+      <c r="A8" s="143"/>
       <c r="B8" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="152"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="154"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="136"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="158"/>
+      <c r="A9" s="143"/>
       <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="163" t="s">
+      <c r="C9" s="148" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="164"/>
-      <c r="E9" s="165"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="150"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="159"/>
+      <c r="A10" s="144"/>
       <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="134" t="s">
+      <c r="C10" s="137" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="135"/>
-      <c r="E10" s="136"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="139"/>
     </row>
     <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="140" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="134" t="s">
+      <c r="C11" s="137" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="135"/>
-      <c r="E11" s="136"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="139"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="156"/>
+      <c r="A12" s="141"/>
       <c r="B12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="134" t="s">
+      <c r="C12" s="137" t="s">
         <v>180</v>
       </c>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="139"/>
     </row>
     <row r="13" spans="1:5" ht="17.25" thickBot="1">
-      <c r="A13" s="157"/>
+      <c r="A13" s="142"/>
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="134" t="s">
+      <c r="C13" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="D13" s="135"/>
-      <c r="E13" s="136"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C11:E11"/>
@@ -49167,14 +49179,6 @@
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -51405,6 +51409,9 @@
       <c r="C61" s="48"/>
       <c r="D61" s="46">
         <v>60063</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>3298</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="17.25">
@@ -61305,6 +61312,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100AC834DCA4512FD4AA91D343FFA7BD938" ma:contentTypeVersion="5" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="a93527defddc8062963a8f9eedd5f2e6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2c4afa66-cfaf-47b2-bbae-a9fa2171cafe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7eecf417e8c6e030f88fe43e3fc321d8" ns2:_="">
     <xsd:import namespace="2c4afa66-cfaf-47b2-bbae-a9fa2171cafe"/>
@@ -61440,15 +61456,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -61459,6 +61466,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A54467A-3F6D-4C2E-B9B5-9AE15DAE2C4C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E753EEF-E8D9-4BC9-81C8-2C84F0D405AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -61472,14 +61487,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A54467A-3F6D-4C2E-B9B5-9AE15DAE2C4C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
